--- a/outputs/40757.xlsx
+++ b/outputs/40757.xlsx
@@ -115,16 +115,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="17" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="17" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -349,70 +353,70 @@
   <dimension ref="A2:B11"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.5"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44764</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44788</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44792</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="0" t="n">
-        <f aca="false">SUMPRODUCT((TEXT($A$3:$A$6,"mmmm")=$A10)*$B$3:$B$6)</f>
+      <c r="B10" s="1" t="n">
+        <f aca="false">SUMPRODUCT((MONTH($A$3:$A$6)=7)*$B$3:$B$6)</f>
         <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="0" t="n">
-        <f aca="false">SUMPRODUCT((TEXT($A$3:$A$6,"mmmm")=$A11)*$B$3:$B$6)</f>
+      <c r="B11" s="1" t="n">
+        <f aca="false">SUMPRODUCT((MONTH($A$3:$A$6)=8)*$B$3:$B$6)</f>
         <v>6</v>
       </c>
     </row>

--- a/outputs/40757.xlsx
+++ b/outputs/40757.xlsx
@@ -108,10 +108,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
@@ -124,11 +121,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="17" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -357,7 +354,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.5"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -365,7 +362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
         <v>44743</v>
       </c>
@@ -373,7 +370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
         <v>44764</v>
       </c>
@@ -381,7 +378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
         <v>44788</v>
       </c>
@@ -389,7 +386,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
         <v>44792</v>
       </c>
@@ -397,12 +394,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -411,7 +408,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
